--- a/data/planning/volume.xlsx
+++ b/data/planning/volume.xlsx
@@ -4171,50 +4171,85 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>work_type_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>received_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sla_deadline_at</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>required_transport_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>service_duration_source</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -4244,50 +4279,85 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4317,50 +4387,85 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -4390,50 +4495,85 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4463,50 +4603,85 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4536,50 +4711,85 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4609,50 +4819,85 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -4682,50 +4927,85 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -4755,50 +5035,85 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -4828,50 +5143,85 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -4901,50 +5251,85 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -4974,50 +5359,85 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -5047,50 +5467,85 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5120,50 +5575,85 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -5193,50 +5683,85 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -5266,50 +5791,85 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -5339,50 +5899,85 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -5412,50 +6007,85 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -5485,50 +6115,85 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -5558,50 +6223,85 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -5631,50 +6331,85 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -5704,50 +6439,85 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -5777,50 +6547,85 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -5850,50 +6655,85 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -5923,50 +6763,85 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -5996,50 +6871,85 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -6069,50 +6979,85 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -6142,50 +7087,85 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -6215,50 +7195,85 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -6288,50 +7303,85 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -6361,50 +7411,85 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -6434,50 +7519,85 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -6507,50 +7627,85 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -6580,50 +7735,85 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -6653,50 +7843,85 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -6726,50 +7951,85 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -6799,50 +8059,85 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -6872,50 +8167,85 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -6945,50 +8275,85 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -7018,50 +8383,85 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -7091,50 +8491,85 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -7164,50 +8599,85 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -7237,50 +8707,85 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -7310,50 +8815,85 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -7383,50 +8923,85 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -7456,50 +9031,85 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -7529,50 +9139,85 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -7602,50 +9247,85 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -7675,50 +9355,85 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -7748,50 +9463,85 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -7821,50 +9571,85 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -16053,25 +17838,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_priority</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>travel_minutes</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>work_minutes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>documents_minutes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>norm_minutes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -16085,25 +17885,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>synthetic_1900_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -16117,25 +17932,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>synthetic_1900_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -16149,25 +17979,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>synthetic_1900_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3</t>
         </is>

--- a/data/planning/volume.xlsx
+++ b/data/planning/volume.xlsx
@@ -4580,85 +4580,120 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>work_type_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>received_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sla_deadline_at</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>required_transport_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>service_duration_source</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>lifecycle_state</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>revision</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>execution_cycle</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>actual_started_at</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>actual_completed_at</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>cancel_reason</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>last_event_id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -4688,85 +4723,120 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4796,85 +4866,120 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -4904,85 +5009,120 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -5012,85 +5152,120 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -5120,85 +5295,120 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -5228,85 +5438,120 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -5336,85 +5581,120 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -5444,85 +5724,120 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -5552,85 +5867,120 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -5660,85 +6010,120 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -5768,85 +6153,120 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -5876,85 +6296,120 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5984,85 +6439,120 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -6092,85 +6582,120 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -6200,85 +6725,120 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -6308,85 +6868,120 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -6416,85 +7011,120 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -6524,85 +7154,120 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -6632,85 +7297,120 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -6740,85 +7440,120 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -6848,85 +7583,120 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -6956,85 +7726,120 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -7064,85 +7869,120 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -7172,85 +8012,120 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -7280,85 +8155,120 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -7388,85 +8298,120 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -7496,85 +8441,120 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -7604,85 +8584,120 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -7712,85 +8727,120 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -7820,85 +8870,120 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -7928,85 +9013,120 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -8036,85 +9156,120 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -8144,85 +9299,120 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -8252,85 +9442,120 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -8360,85 +9585,120 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -8468,85 +9728,120 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -8576,85 +9871,120 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -8684,85 +10014,120 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -8792,85 +10157,120 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -8900,85 +10300,120 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -9008,85 +10443,120 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -9116,85 +10586,120 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -9224,85 +10729,120 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -9332,85 +10872,120 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -9440,85 +11015,120 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -9548,85 +11158,120 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -9656,85 +11301,120 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -9764,85 +11444,120 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -9872,85 +11587,120 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -9980,85 +11730,120 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -18880,25 +20665,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_priority</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>travel_minutes</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>work_minutes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>documents_minutes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>norm_minutes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -18912,25 +20712,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>synthetic_1900_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -18944,25 +20759,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>synthetic_1900_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -18976,25 +20806,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>synthetic_1900_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3</t>
         </is>

--- a/data/planning/volume.xlsx
+++ b/data/planning/volume.xlsx
@@ -30,14 +30,13 @@
     <sheet name="brigades" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="notification_events" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="ticket_appliances" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="ticket_assignments" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ticket_comments" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="work_events" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="worker_day_states" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="brigade_members" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="day_plan_revisions" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="equipment_movements" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="routes" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ticket_comments" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="work_events" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="worker_day_states" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="brigade_members" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="day_plan_revisions" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="equipment_movements" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="routes" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4625,75 +4624,85 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>assigned_worker_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>is_pinned</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>revision</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>execution_cycle</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>actual_started_at</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>actual_completed_at</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cancel_reason</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>last_event_id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -4768,52 +4777,52 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -4828,15 +4837,25 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4911,52 +4930,52 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -4971,15 +4990,25 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -5054,52 +5083,52 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -5114,15 +5143,25 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -5197,52 +5236,52 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -5257,15 +5296,25 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -5340,52 +5389,52 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -5400,15 +5449,25 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -5483,52 +5542,52 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -5543,15 +5602,25 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -5626,52 +5695,52 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -5686,15 +5755,25 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -5769,52 +5848,52 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -5829,15 +5908,25 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -5912,52 +6001,52 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -5972,15 +6061,25 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -6055,52 +6154,52 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -6115,15 +6214,25 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -6198,52 +6307,52 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -6258,15 +6367,25 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -6341,52 +6460,52 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6401,15 +6520,25 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -6484,52 +6613,52 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6544,15 +6673,25 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -6627,52 +6766,52 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6687,15 +6826,25 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -6770,52 +6919,52 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6830,15 +6979,25 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -6913,52 +7072,52 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -6973,15 +7132,25 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -7056,52 +7225,52 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7116,15 +7285,25 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -7199,52 +7378,52 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -7259,15 +7438,25 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -7342,52 +7531,52 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -7402,15 +7591,25 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -7485,52 +7684,52 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -7545,15 +7744,25 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -7628,52 +7837,52 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -7688,15 +7897,25 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -7771,52 +7990,52 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -7831,15 +8050,25 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -7914,52 +8143,52 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -7974,15 +8203,25 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -8057,52 +8296,52 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -8117,15 +8356,25 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -8200,52 +8449,52 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -8260,15 +8509,25 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -8343,52 +8602,52 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -8403,15 +8662,25 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -8486,52 +8755,52 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -8546,15 +8815,25 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -8629,52 +8908,52 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -8689,15 +8968,25 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -8772,52 +9061,52 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -8832,15 +9121,25 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -8915,52 +9214,52 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -8975,15 +9274,25 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -9058,52 +9367,52 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -9118,15 +9427,25 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -9201,52 +9520,52 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -9261,15 +9580,25 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -9344,52 +9673,52 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -9404,15 +9733,25 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -9487,52 +9826,52 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R35" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -9547,15 +9886,25 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -9630,52 +9979,52 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R36" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -9690,15 +10039,25 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -9773,52 +10132,52 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R37" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -9833,15 +10192,25 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -9916,52 +10285,52 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R38" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -9976,15 +10345,25 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -10059,52 +10438,52 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R39" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -10119,15 +10498,25 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -10202,52 +10591,52 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R40" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -10262,15 +10651,25 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -10345,52 +10744,52 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R41" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -10405,15 +10804,25 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -10488,52 +10897,52 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R42" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -10548,15 +10957,25 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -10631,52 +11050,52 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R43" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -10691,15 +11110,25 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -10774,52 +11203,52 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R44" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -10834,15 +11263,25 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -10917,52 +11356,52 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -10977,15 +11416,25 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -11060,52 +11509,52 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R46" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -11120,15 +11569,25 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -11203,52 +11662,52 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R47" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -11263,15 +11722,25 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -11346,52 +11815,52 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R48" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -11406,15 +11875,25 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -11489,52 +11968,52 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R49" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -11549,15 +12028,25 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -11632,52 +12121,52 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R50" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -11692,15 +12181,25 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -11775,52 +12274,52 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R51" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -11835,15 +12334,25 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -18390,12 +18899,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>author_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>assigned_at</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -18415,32 +18939,164 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>ticket_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>author_id</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>worker_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>route_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>occurred_at</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>recorded_at</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>actor_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>previous_state</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>new_state</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>before_revision</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>after_revision</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>idempotency_key</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>new_ticket</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2030-01-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>waiting_assignment</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>synthetic-1900-ticket-1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{"ticket_id":1}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -18460,77 +19116,77 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>worker_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ticket_id</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>route_date</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>district_id</t>
+          <t>revision</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>route_date</t>
+          <t>available</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>occurred_at</t>
+          <t>unavailable_at</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>recorded_at</t>
+          <t>unavailable_until</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>actor_id</t>
+          <t>last_location_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>current_ticket_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>current_destination_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>en_route_started_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>expected_available_at</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>previous_state</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>new_state</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>before_revision</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>after_revision</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>idempotency_key</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
@@ -18542,7 +19198,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>new_ticket</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18552,7 +19208,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2030-01-15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -18562,17 +19218,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2030-01-15</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -18592,7 +19248,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>waiting_assignment</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -18602,17 +19258,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>synthetic-1900-ticket-1</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{"ticket_id":1}</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -18637,164 +19293,252 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>brigade_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>worker_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>district_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>route_date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>revision</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>unavailable_at</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>unavailable_until</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>last_location_id</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>current_ticket_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>current_destination_id</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>en_route_started_at</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>expected_available_at</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2030-01-15</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1</t>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -18814,12 +19558,62 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>brigade_id</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>route_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>revision</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>previous_revision</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>actor_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fingerprint</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>is_current</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -18831,235 +19625,57 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>28</t>
+          <t>2030-01-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>037af78dc92cfa511d01a1148b4013f72d2ef1c959523e157a79e73e128339a2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -19079,22 +19695,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>district_id</t>
+          <t>ticket_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>route_date</t>
+          <t>execution_cycle</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>revision</t>
+          <t>appliance_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>previous_revision</t>
+          <t>office_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -19104,35 +19720,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>actor_id</t>
+          <t>movement</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>fingerprint</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_current</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -19146,7 +19747,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2030-01-15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -19156,7 +19757,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19166,35 +19767,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>consume</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>037af78dc92cfa511d01a1148b4013f72d2ef1c959523e157a79e73e128339a2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19277,113 +19863,6 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ticket_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>execution_cycle</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>appliance_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>office_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>movement</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>consume</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
           <t>worker_id</t>
         </is>
       </c>
